--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
@@ -47,7 +47,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -57,11 +57,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8EEF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,9 +101,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1339,21 +1331,25 @@
       <c r="F16" s="4" t="n">
         <v>912138081</v>
       </c>
-      <c r="G16" s="7" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Qashqadaryo, Yakkabog' tumani</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>75-sonli umumiy o'rta ta'lim maktabi</t>
+          <t>Yakkabog' tumani 75-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>General Secondary School No. 75</t>
+          <t>General Secondary School No. 75, Yakkabog District</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>Общеобразовательная школа №75</t>
+          <t>Общеобразовательная школа №75 Яккабагского района</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,37 +27,15 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color rgb="001E3A8A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -86,22 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -467,2034 +435,1874 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A3:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4.5" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="17.5" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16.5" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="3.14" customWidth="1" min="1" max="1"/>
+    <col width="34.43" customWidth="1" min="2" max="2"/>
+    <col width="17.29" customWidth="1" min="3" max="3"/>
+    <col width="13.43" customWidth="1" min="4" max="4"/>
+    <col width="17.86" customWidth="1" min="5" max="5"/>
+    <col width="22.57" customWidth="1" min="6" max="6"/>
+    <col width="21.71" customWidth="1" min="7" max="7"/>
+    <col width="17.71" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="26.29" customWidth="1" min="10" max="10"/>
+    <col width="13.86" customWidth="1" min="11" max="11"/>
+    <col width="16.43" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Guruh 26-05 (32 nafar)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Namuna: Saydalimov Anvarjon Sarvarjon o`g`li | 517******0016 | AC1686958 | 990201527 | Qashqadaryo, Qarshi | 4-mittituman 21/23 | Qarshi shahar 1-maktab | Qarshi City School No. 1 | Школа №1 города Карши | Maktab | AA1775603 | 2008-2019</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="63" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Avval o`qigan muassasa nomi(Rus tilida)</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="n">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>60609085720090</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>AE4148917</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="2" t="n">
         <v>918715737</v>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 109-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 109, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №109 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>UM 03719993</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="n">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>60409085680037</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>AE4831229</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="2" t="n">
         <v>333890503</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="2" t="n">
         <v>949791283</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №46 Китабского района</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>UM 03729337</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="4" t="n">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>62311065590082</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>AD6820021</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="2" t="n">
         <v>876360708</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="2" t="n">
         <v>976363774</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>UM 03297113</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>60904075680023</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>AD9709558</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="2" t="n">
         <v>774231707</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="2" t="n">
         <v>956162509</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №21 Китабского района</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>UM 03273940</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>62802085590063</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>AD9654318</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="2" t="n">
         <v>883090228</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="2" t="n">
         <v>886177808</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son politexnikumi</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Polytechnic College No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Политехникум №2 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>PT 0017576</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>61803085680050</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>AE2374828</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="2" t="n">
         <v>914551195</v>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 2-son texnikumi</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 2, Kitob District</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Техникум №2 Китабского района</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>PT 0030461</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>61306045630044</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AD0697178</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="2" t="n">
         <v>881009504</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="2" t="n">
         <v>976325574</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Qamashi tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 11, Qamashi District</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №11 Камашинского района</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>UM 1283543</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="4" t="n">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>60208085590146</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>AE3497923</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="2" t="n">
         <v>887381981</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="2" t="n">
         <v>957401981</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №43 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>UM 03754785</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>60710085680054</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>AD9335686</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="2" t="n">
         <v>886199703</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="2" t="n">
         <v>876295108</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 51, Kitob District</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №51 Китабского района</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>UM 03729467</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>61510085680048</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>AE4255446</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="2" t="n">
         <v>936367986</v>
       </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №21 Китабского района</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>UM 03728624</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>60211085680014</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>AE4319796</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="2" t="n">
         <v>976180259</v>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №6 Китабского района</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>UM 03728207</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>61701005680057</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AB6258375</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="2" t="n">
         <v>978577404</v>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Qarshi Pedagogical College</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Каршинский педагогический колледж</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>K 0349228</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>62512075730060</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>AD9394305</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="2" t="n">
         <v>946034407</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="2" t="n">
         <v>912138081</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 75-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 75, Yakkabog District</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №75 Яккабагского района</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>UM 03301327</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>61611085680042</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>AE4290181</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="2" t="n">
         <v>701206508</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="2" t="n">
         <v>995698112</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №46 Китабского района</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>UM 03729343</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>41902975680049</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>AD7829399</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob Agro-Industrial Vocational College</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>Китабский агропромышленный профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>K 0236649</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>62112085680050</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>AE2895049</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="2" t="n">
         <v>886030021</v>
       </c>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Kitob District</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №8 Китабского района</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>UM 03753455</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>62710075590066</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>AD9123240</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="2" t="n">
         <v>701885432</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="2" t="n">
         <v>958050186</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 1-son politexnikumi</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Polytechnic College No. 1, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>Политехникум №1 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>PT 0257899</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Nazarova Munisa Erkin qizi</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>41205925680015</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>AE7685867</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="2" t="n">
         <v>919571858</v>
       </c>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Kitob tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>General Secondary School No. 29, Kitob District</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>UM 1174926</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2010-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Ne'matova Sevinch Hikmatullo qizi</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>60212085680048</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>AE7082532</t>
         </is>
       </c>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №1 Китабского района</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>UM 03727760</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="4" t="n">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>61809085680096</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>AE4817469</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="2" t="n">
         <v>973889978</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="2" t="n">
         <v>880407877</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Kitob District</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №20 Китабского района</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>UM 03728575</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Omonova Charos Orif qizi</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>40306985590014</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>AE1338424</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="2" t="n">
         <v>919491627</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="2" t="n">
         <v>900698998</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Agro-Industrial Vocational College</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>Шахрисабзский агропромышленный профессиональный колледж</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>K 5023908</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Oripova Sevinch G'olib qizi</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>62007085680095</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>AE3333890</t>
         </is>
       </c>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №45 Китабского района</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>UM 03729323</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="4" t="n">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>60803075590140</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>AD6663341</t>
         </is>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="2" t="n">
         <v>995240810</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="2" t="n">
         <v>955248180</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 66-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 66, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №66 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>UM 03298601</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="n">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>60511085680024</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>AE6043288</t>
         </is>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="2" t="n">
         <v>773900314</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="2" t="n">
         <v>779656308</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 85, Kitob District</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №85 Китабского района</t>
-        </is>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>UM 03730668</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="4" t="n">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>62307095590022</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>AE5776687</t>
         </is>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="2" t="n">
         <v>919614037</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="2" t="n">
         <v>918021670</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №1 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>UM 03751494</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="4" t="n">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>62803055590089</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>AD0914473</t>
         </is>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="2" t="n">
         <v>908942471</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="2" t="n">
         <v>919496471</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Specialized School No. 14 with In-Depth Study of Certain Subjects, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Специализированная школа №14 с углублённым изучением отдельных предметов города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>UM 1319051</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="4" t="n">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>61407075590019</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>AD6026687</t>
         </is>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="2" t="n">
         <v>919600814</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="2" t="n">
         <v>912250767</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №15 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>UM 02172465</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="4" t="n">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>62710085680012</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>AE5949204</t>
         </is>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Китабского района</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>UM 03730083</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="4" t="n">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>62710085680029</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>AE5949016</t>
         </is>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №70 Китабского района</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>UM 03730084</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="4" t="n">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>61810085590061</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>AE4384190</t>
         </is>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="2" t="n">
         <v>870004608</v>
       </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Общеобразовательная школа №26 Шахрисабзского района</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>UM 03754097</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="4" t="n">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>42601955730024</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>AD8362477</t>
         </is>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="2" t="n">
         <v>995590930</v>
       </c>
-      <c r="F34" s="4" t="n"/>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog Vocational College of Consumer Services</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Яккабагский профессиональный колледж бытового обслуживания</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>K 3418837</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>2011-2014</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="4" t="n">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>61309085590066</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>AE1419035</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="2" t="n">
         <v>914551195</v>
       </c>
-      <c r="F35" s="4" t="n"/>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son texnikumi</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>Техникум №2 города Шахрисабз</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>PT 0339260</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
@@ -435,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:M35"/>
+  <dimension ref="A3:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.14" customWidth="1" min="1" max="1"/>
-    <col width="34.43" customWidth="1" min="2" max="2"/>
-    <col width="17.29" customWidth="1" min="3" max="3"/>
-    <col width="13.43" customWidth="1" min="4" max="4"/>
-    <col width="17.86" customWidth="1" min="5" max="5"/>
-    <col width="22.57" customWidth="1" min="6" max="6"/>
-    <col width="21.71" customWidth="1" min="7" max="7"/>
-    <col width="17.71" customWidth="1" min="8" max="8"/>
-    <col width="36" customWidth="1" min="9" max="9"/>
-    <col width="26.29" customWidth="1" min="10" max="10"/>
-    <col width="13.86" customWidth="1" min="11" max="11"/>
-    <col width="16.43" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34.43" customWidth="1" min="3" max="3"/>
+    <col width="17.29" customWidth="1" min="4" max="4"/>
+    <col width="13.43" customWidth="1" min="5" max="5"/>
+    <col width="17.86" customWidth="1" min="6" max="6"/>
+    <col width="22.57" customWidth="1" min="7" max="7"/>
+    <col width="21.71" customWidth="1" min="8" max="8"/>
+    <col width="17.71" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="26.29" customWidth="1" min="11" max="11"/>
+    <col width="13.86" customWidth="1" min="12" max="12"/>
+    <col width="16.43" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="3" ht="47.25" customHeight="1">
@@ -461,60 +462,65 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>Guruhi</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>F.I.O</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>JSHSHIR</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Pasport seriya raqami</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>2-Tel raqam(pastdagi shablondagidek kiritilsin)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>Yashash viloyat+tumani</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>UY manzili</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Uzbek tilida)</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Avval o`qigan muassasa nomi(Ingliz tilida)</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Maktab, kollej va HK</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>Avval olgan diplom seriya+raqami</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>Boshlagan va tugatgan yili</t>
         </is>
@@ -526,50 +532,55 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>60609085720090</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>AE4148917</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>918715737</v>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 109-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 109, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>UM 03719993</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -581,52 +592,57 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>Ahmadova Munisa Bekzod qizi</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>60409085680037</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>AE4831229</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>333890503</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>949791283</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>UM 03729337</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -638,52 +654,57 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>62311065590082</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>AD6820021</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>876360708</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>976363774</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>UM 03297113</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -695,52 +716,57 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>Berdimurodova Nafosat Javlon qizi</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>60904075680023</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>AD9709558</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>774231707</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>956162509</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>UM 03273940</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -752,52 +778,57 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>Choriyeva Zahro Xayrullo qizi</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>62802085590063</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>AD9654318</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>883090228</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>886177808</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son politexnikumi</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Polytechnic College No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>PT 0017576</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
@@ -809,50 +840,55 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>Ergasheva Shabbona Shodmon qizi</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>61803085680050</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AE2374828</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>914551195</v>
       </c>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 2-son texnikumi</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 2, Kitob District</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>PT 0030461</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>
@@ -864,52 +900,57 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>61306045630044</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>AD0697178</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>881009504</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>976325574</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qamashi tumani</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n"/>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Qamashi tumani 11-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 11, Qamashi District</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>UM 1283543</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
@@ -921,52 +962,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>G'ayratova Jasmina Sherali qizi</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>60208085590146</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>AE3497923</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>887381981</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>957401981</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n"/>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 43, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>UM 03754785</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -978,52 +1024,57 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>Ixtiyorova Niginabonu Xolovna</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>60710085680054</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>AD9335686</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>886199703</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>876295108</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 51, Kitob District</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>UM 03729467</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1035,50 +1086,55 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>61510085680048</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>AE4255446</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>936367986</v>
       </c>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 21, Kitob District</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>UM 03728624</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1090,50 +1146,55 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>60211085680014</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>AE4319796</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>976180259</v>
       </c>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 6, Kitob District</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>UM 03728207</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1145,50 +1206,55 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>Jumayeva Muxlisa Komiljon qizi</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>61701005680057</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>AB6258375</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>978577404</v>
       </c>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Qarshi tumani</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>Qarshi Pedagogical College</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>K 0349228</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>2016-2019</t>
         </is>
@@ -1200,52 +1266,57 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>Jurayeva Madina Odil qizi</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>62512075730060</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>AD9394305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="F16" s="2" t="n">
         <v>946034407</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>912138081</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 75-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 75, Yakkabog District</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>UM 03301327</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -1257,52 +1328,57 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>Luxmonova Nozima Ilhom qizi</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>61611085680042</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>AE4290181</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="F17" s="2" t="n">
         <v>701206508</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>995698112</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 46, Kitob District</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>UM 03729343</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1314,48 +1390,53 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>Muhammadiyeva Gulbahor Uchqun qizi</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>41902975680049</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>AD7829399</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Kitob Agro-Industrial Vocational College</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>K 0236649</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
@@ -1367,50 +1448,55 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>Murodova Munisa Muxtor qizi</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>62112085680050</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>AE2895049</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="F19" s="2" t="n">
         <v>886030021</v>
       </c>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 8, Kitob District</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>UM 03753455</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1422,52 +1508,57 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>Muzrapova Ruhshona Asrorxon qizi</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>62710075590066</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>AD9123240</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="F20" s="2" t="n">
         <v>701885432</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>958050186</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 1-son politexnikumi</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Polytechnic College No. 1, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>PT 0257899</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2022-2025</t>
         </is>
@@ -1479,50 +1570,55 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>Nazarova Munisa Erkin qizi</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>41205925680015</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>AE7685867</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="F21" s="2" t="n">
         <v>919571858</v>
       </c>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 29, Kitob District</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>UM 1174926</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>2010-2021</t>
         </is>
@@ -1534,48 +1630,53 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>Ne'matova Sevinch Hikmatullo qizi</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>60212085680048</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>AE7082532</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H22" s="2" t="n"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Kitob District</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>UM 03727760</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1587,52 +1688,57 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>Normurodova Gulsanam Elyor qizi</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>61809085680096</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>AE4817469</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="F23" s="2" t="n">
         <v>973889978</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>880407877</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 20, Kitob District</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>UM 03728575</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1644,52 +1750,57 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>Omonova Charos Orif qizi</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>40306985590014</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>AE1338424</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="F24" s="2" t="n">
         <v>919491627</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>900698998</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz Agro-Industrial Vocational College</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>K 5023908</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>2013-2016</t>
         </is>
@@ -1701,48 +1812,53 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>Oripova Sevinch G'olib qizi</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>62007085680095</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>AE3333890</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 45-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 45, Kitob District</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>UM 03729323</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1754,52 +1870,57 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>Ozodova Klara Fayzullayevna</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>60803075590140</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>AD6663341</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="F26" s="2" t="n">
         <v>995240810</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>955248180</v>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 66-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 66, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>UM 03298601</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>2014-2025</t>
         </is>
@@ -1811,52 +1932,57 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>Saidova Dilso'z Ilyos qizi</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>60511085680024</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>AE6043288</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="F27" s="2" t="n">
         <v>773900314</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>779656308</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 85-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 85, Kitob District</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>UM 03730668</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1868,52 +1994,57 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>Sharipova Diyora Jasur qizi</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>62307095590022</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>AE5776687</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="F28" s="2" t="n">
         <v>919614037</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>918021670</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 1, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>UM 03751494</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -1925,52 +2056,57 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>Toshmurodova Sarvara Ilxom qizi</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>62803055590089</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>AD0914473</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="F29" s="2" t="n">
         <v>908942471</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>919496471</v>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Specialized School No. 14 with In-Depth Study of Certain Subjects, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>UM 1319051</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>2011-2022</t>
         </is>
@@ -1982,52 +2118,57 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>Tursunova Aziza Anvarovna</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>61407075590019</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>AD6026687</t>
         </is>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="F30" s="2" t="n">
         <v>919600814</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>912250767</v>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 15, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>UM 02172465</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>2013-2024</t>
         </is>
@@ -2039,50 +2180,55 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>Tursunova Fotima Qosim qizi</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>62710085680012</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>AE5949204</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="F31" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>UM 03730083</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2094,50 +2240,55 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>Tursunova Zuhra Qosim qizi</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>62710085680029</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>AE5949016</t>
         </is>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="F32" s="2" t="n">
         <v>995658681</v>
       </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 70, Kitob District</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>UM 03730084</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2149,50 +2300,55 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>Usmonova Sabrina Baxtiyor qizi</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>61810085590061</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>AE4384190</t>
         </is>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="F33" s="2" t="n">
         <v>870004608</v>
       </c>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>General Secondary School No. 26, Shahrisabz District</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Maktab</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>UM 03754097</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>2015-2026</t>
         </is>
@@ -2204,50 +2360,55 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>Xolmirzayeva Zebuniso Xushvaq qizi</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>42601955730024</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>AD8362477</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="F34" s="2" t="n">
         <v>995590930</v>
       </c>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' maishiy xizmat kasb-hunar kolleji</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog Vocational College of Consumer Services</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Kollej</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>K 3418837</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>2011-2014</t>
         </is>
@@ -2259,50 +2420,55 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>26-05</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>Yuldosheva Ruhshona Xabibullo qizi</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>61309085590066</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>AE1419035</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>914551195</v>
       </c>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son texnikumi</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Technical School No. 2, Shahrisabz City</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Texnikum</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>PT 0339260</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>2023-2026</t>
         </is>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>333890503</v>
+        <v>338905030</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>949791283</v>
@@ -621,7 +621,11 @@
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Oq suv MFY, Nimgi koʻchasi, 69-uy</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
@@ -735,17 +739,21 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>774231707</v>
+        <v>743217070</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>956162509</v>
+        <v>561635090</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Bektemir MFY, Shifokorlar kuchasi, 238-uy</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
@@ -797,17 +805,21 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>883090228</v>
+        <v>830902280</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>886177808</v>
+        <v>800578080</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>G'alaba MFY, Firdavsiy ko'chasi, 12/2-uy</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son politexnikumi</t>
@@ -859,15 +871,21 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>914551195</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
+        <v>840204080</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>990630419</v>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Navbahor MFY, Eski Jilisuv 3 qishlog‘i, 92-uy</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 2-son texnikumi</t>
@@ -981,17 +999,21 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>887381981</v>
+        <v>762945080</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>957401981</v>
+        <v>873819820</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Toʻdamaydon, Fidokor, 92.0</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 43-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1043,17 +1065,21 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>886199703</v>
+        <v>818311670</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>876295108</v>
+        <v>183116787</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Iskana MFY, Iskana ko'chasi, 40-uy</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 51-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1105,15 +1131,21 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>936367986</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
+        <v>793476080</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>914564661</v>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>BektimirMFY, Yoshlar kuchasi, 27.0</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 21-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1225,15 +1257,21 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>978577404</v>
-      </c>
-      <c r="G15" s="2" t="n"/>
+        <v>978527404</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>785274040</v>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Qarshi tumani</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Katlos mfy, Obigarm kuchasi, 89.0</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Qarshi pedagogika kolleji</t>
@@ -1285,17 +1323,21 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>946034407</v>
+        <v>460344070</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>912138081</v>
+        <v>30150780</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Chumich MFY, Ayg'irkul ko'chasi, 42-uy</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' tumani 75-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1408,14 +1450,22 @@
           <t>AD7829399</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
+      <c r="F18" s="2" t="n">
+        <v>940693027</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>940693027</v>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Shurabsoy MFY, Boshchil qishlogʼi, 68-uy</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Kitob agrosanoat kasb-hunar kolleji</t>
@@ -1467,15 +1517,21 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>886030021</v>
-      </c>
-      <c r="G19" s="2" t="n"/>
+        <v>881796080</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>530860888</v>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Miraki mfy, Navoiy ko'chasi, 68.0</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 8-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1648,14 +1704,22 @@
           <t>AE7082532</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
+        <v>107102830</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>107102830</v>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Hamid Olimjon MFY, Amir Temur, 69.0</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1707,17 +1771,21 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>973889978</v>
+        <v>738899780</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>880407877</v>
+        <v>755860880</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Alaquyliq MFY, Tutzoz kuchasi, 16-uy</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 20-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1889,17 +1957,21 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>995240810</v>
+        <v>910608100</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>955248180</v>
+        <v>781800701</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Sayyod MFY, Obod mahallasi, 13.0</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 66-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1951,17 +2023,21 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>773900314</v>
+        <v>796563080</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>779656308</v>
+        <v>713906770</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Surum mahallasi, Sokin koʻchasi, 66.0</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 85-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2013,17 +2089,21 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
+        <v>180216700</v>
+      </c>
+      <c r="G28" s="2" t="n">
         <v>919614037</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>918021670</v>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Sinabog’ MFY, Shoxsaroy ko’chasi, 205-uy</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 1-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2075,17 +2155,21 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>908942471</v>
+        <v>86424710</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>919496471</v>
+        <v>194964710</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Shahrisabz shahri</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Dustlik mahallasi, Bunyodkor kuchasi, 97.0</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 14-sonli ayrim fanlar chuqur o'rganiladigan ixtisoslashtirilgan maktabi</t>
@@ -2137,17 +2221,21 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>919600814</v>
+        <v>196008140</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>912250767</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Zingiron MFY, Zingiron ko'chasi, 46-uy</t>
+        </is>
+      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 15-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2199,15 +2287,21 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>995658681</v>
-      </c>
-      <c r="G31" s="2" t="n"/>
+        <v>780982300</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>956586810</v>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Navbahor MFY, Yangi jilisuv qishlogʻi, 99 uy</t>
+        </is>
+      </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2259,15 +2353,21 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>995658681</v>
-      </c>
-      <c r="G32" s="2" t="n"/>
+        <v>780981300</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>956586810</v>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Jilisuv MFY, Yangi Jilisuv, 99.0</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 70-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2319,15 +2419,21 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>870004608</v>
-      </c>
-      <c r="G33" s="2" t="n"/>
+        <v>700046080</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>771088048</v>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrisabz shahri</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Bogʻishamol MFY, Oʻzbekiston koʻchasi, 15-uy</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz tumani 26-sonli umumiy o'rta ta'lim maktabi</t>
@@ -2381,13 +2487,19 @@
       <c r="F34" s="2" t="n">
         <v>995590930</v>
       </c>
-      <c r="G34" s="2" t="n"/>
+      <c r="G34" s="2" t="n">
+        <v>518201950</v>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Yakkabog' tumani</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Yangiobod mahhalla, Ezgulik kuchasi, 17B</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Yakkabog' maishiy xizmat kasb-hunar kolleji</t>
@@ -2439,15 +2551,21 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>914551195</v>
-      </c>
-      <c r="G35" s="2" t="n"/>
+        <v>48913000</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>908708827</v>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tumani</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Yangi obod MFY, Yangi obod 11/5, 11/5</t>
+        </is>
+      </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 2-son texnikumi</t>

--- a/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
+++ b/hisobotlar/qabul/guruhlar/QABUL - 2026 (26-05).xlsx
@@ -551,15 +551,21 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>918715737</v>
-      </c>
-      <c r="G4" s="2" t="n"/>
+        <v>770069149</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>909604580</v>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
+          <t>Qashqadaryo, Chiroqchi tumani</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Taragʻay MFY, Taragʻay, Yuq</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 109-sonli umumiy o'rta ta'lim maktabi</t>
@@ -611,7 +617,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>338905030</v>
+        <v>333890503</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>949791283</v>
@@ -739,14 +745,14 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>743217070</v>
+        <v>774321707</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>561635090</v>
+        <v>956163509</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -805,14 +811,14 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>830902280</v>
+        <v>883090228</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>800578080</v>
+        <v>880057808</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -871,7 +877,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>840204080</v>
+        <v>884020408</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>990630419</v>
@@ -999,19 +1005,19 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>762945080</v>
+        <v>957401981</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>873819820</v>
+        <v>957401981</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Toʻdamaydon, Fidokor, 92.0</t>
+          <t>Toʻdamaydon, Fidokor, 92-uy</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,19 +1071,19 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>818311670</v>
+        <v>876295108</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>183116787</v>
+        <v>881831167</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
+          <t>Qashqadaryo, Kitob</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Iskana MFY, Iskana ko'chasi, 40-uy</t>
+          <t>Iksana MFY, Iskana qishloqi, 40-uy</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1131,7 +1137,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>793476080</v>
+        <v>879347608</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>914564661</v>
@@ -1143,7 +1149,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>BektimirMFY, Yoshlar kuchasi, 27.0</t>
+          <t>BektimirMFY, Yoshlar kuchasi, 27-uy</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1197,15 +1203,21 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
+        <v>778181856</v>
+      </c>
+      <c r="G14" s="2" t="n">
         <v>976180259</v>
       </c>
-      <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Beshariq MFY, Mehrobod, 45-uy</t>
+        </is>
+      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 6-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1260,7 +1272,7 @@
         <v>978527404</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>785274040</v>
+        <v>978527404</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -1269,7 +1281,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Katlos mfy, Obigarm kuchasi, 89.0</t>
+          <t>Katlos mfy, Obigarm kuchasi, 89-uy</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1323,10 +1335,10 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>460344070</v>
+        <v>946034407</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>30150780</v>
+        <v>903015078</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1392,14 +1404,18 @@
         <v>701206508</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>995698112</v>
+        <v>995688112</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Qashqadaryo, Kitob tumani</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Oqsuv MFY, Nimgi qishloq, 152-uy</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 46-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1517,19 +1533,19 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>881796080</v>
+        <v>888179608</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>530860888</v>
+        <v>950753086</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Miraki mfy, Navoiy ko'chasi, 68.0</t>
+          <t>Miraki mfy, Navoiy ko'chasi, 68-uy</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1583,17 +1599,21 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>701885432</v>
+        <v>778380748</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>958050186</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t>Qashqadaryo, Shahrissbz tumani</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Zangi, Keldihayot koʻchasi 290, 290-uy</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz shahri 1-son politexnikumi</t>
@@ -1647,13 +1667,19 @@
       <c r="F21" s="2" t="n">
         <v>919571858</v>
       </c>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="2" t="n">
+        <v>970340530</v>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Kitob tumani</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
+          <t>Qashqadaryo, Kitob tuman</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Hamid Olimjon, Zilol buloq, 17-uy</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Kitob tumani 29-sonli umumiy o'rta ta'lim maktabi</t>
@@ -1705,10 +1731,10 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>107102830</v>
+        <v>910710283</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>107102830</v>
+        <v>910710283</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -1717,7 +1743,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Hamid Olimjon MFY, Amir Temur, 69.0</t>
+          <t>Hamid Olimjon MFY, Amir Temur, 69-uy</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1771,10 +1797,10 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>738899780</v>
+        <v>973889978</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>755860880</v>
+        <v>908775586</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1837,17 +1863,21 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>919491627</v>
+        <v>900698998</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>900698998</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n"/>
+          <t>Qashqadaryo, Shaxresabiz tumani</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Quchi MFY, Quchi kuchasi, 56-uy</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Shahrisabz agrosanoat kasb-hunar kolleji</t>
@@ -1957,19 +1987,19 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>910608100</v>
+        <v>991060810</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>781800701</v>
+        <v>955278180</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Sayyod MFY, Obod mahallasi, 13.0</t>
+          <t>Sayyod MFY, Obod mahallasi, 13-uy</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2023,10 +2053,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>796563080</v>
+        <v>779656308</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>713906770</v>
+        <v>971390677</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2035,7 +2065,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Surum mahallasi, Sokin koʻchasi, 66.0</t>
+          <t>Surum mahallasi, Sokin koʻchasi, 66-uy</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2089,7 +2119,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>180216700</v>
+        <v>918021670</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>919614037</v>
@@ -2155,19 +2185,19 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>86424710</v>
+        <v>908642471</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>194964710</v>
+        <v>919496471</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Dustlik mahallasi, Bunyodkor kuchasi, 97.0</t>
+          <t>Dustlik MFY, Bunyodkor kuchasi, 97-uy</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2221,14 +2251,14 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>196008140</v>
+        <v>919600814</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>912250767</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz shahar</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2287,10 +2317,10 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>780982300</v>
+        <v>778098130</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>956586810</v>
+        <v>995658681</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2299,7 +2329,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Navbahor MFY, Yangi jilisuv qishlogʻi, 99 uy</t>
+          <t>Jilisuv MFY, Yangi Jilisuv, 99-uy</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2353,10 +2383,10 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>780981300</v>
+        <v>778098230</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>956586810</v>
+        <v>995658681</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2365,7 +2395,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Jilisuv MFY, Yangi Jilisuv, 99.0</t>
+          <t>Navbahor MFY, Yangi jilisuv qishlogʻi, 99 uy</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2419,14 +2449,14 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>700046080</v>
+        <v>870004608</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>771088048</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Shahrisabz shahri</t>
+          <t>Qashqadaryo, Shahrisabz tumani</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -2488,11 +2518,11 @@
         <v>995590930</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>518201950</v>
+        <v>951820195</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Qashqadaryo, Yakkabog' tumani</t>
+          <t>Qashqadaryo, Yakkabogʻ tumani</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2551,7 +2581,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>48913000</v>
+        <v>904891300</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>908708827</v>
